--- a/artfynd/S 2201-2022 artfynd.xlsx
+++ b/artfynd/S 2201-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811763</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976461</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811638</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976460</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811646</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811647</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811710</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811788</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811789</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976463</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976496</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976517</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2103,6 +2168,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976520</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811583</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976436</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976492</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2532,6 +2617,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811328</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2635,6 +2725,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811329</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2747,6 +2842,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976489</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2859,6 +2959,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976499</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2971,8 +3076,36 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88976515</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>